--- a/tutorials/YAMH.xlsx
+++ b/tutorials/YAMH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dbw209/Library/Mobile Documents/com~apple~CloudDocs/Documents/Research/systemdynamics/tutorials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB219E5-8EDC-3346-AD69-8FE32CC613ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51BA1BB-BE2C-D14F-83F7-4194B188229F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elements" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="45">
   <si>
     <t>Label</t>
   </si>
@@ -3494,89 +3494,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="64" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="28" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="28" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="3"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="B3" s="3"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
